--- a/assets/docs/lop3/Am nhac - Lop 3.xlsx
+++ b/assets/docs/lop3/Am nhac - Lop 3.xlsx
@@ -644,7 +644,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 1: Lễ hội âm thanh (Tiết 4)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -787,7 +787,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 2: Em yêu Tổ quốc Việt Nam (Tiết 4)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 3: Vui đến trường (Tiết 4)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 4: Em yêu làn điệu dân ca (Tiết 4)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 5: Đón xuân về (Tiết 4)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 6: Đẹp mãi tuổi thơ (Tiết 4)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Tổ chức hoạt động Vận dụng – Sáng tạo — Chủ đề 7: Âm nhạc nước ngoài (Tiết 4)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">

--- a/assets/docs/lop3/Am nhac - Lop 3.xlsx
+++ b/assets/docs/lop3/Am nhac - Lop 3.xlsx
@@ -803,7 +803,7 @@
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 2.2 CB1a: HS nhận xét nhóm bạn bằng một lời khen và một lời góp ý.
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng.</t>
         </is>
       </c>
     </row>
